--- a/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260910.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260910.xlsx
@@ -1173,17 +1173,17 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>994,822</t>
+          <t>1,988,587</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -1195,17 +1195,17 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>1,988,587</t>
+          <t>994,822</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -1305,17 +1305,17 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>1,819,000</t>
+          <t>373,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1327,17 +1327,17 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>373,000</t>
+          <t>1,819,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -1349,17 +1349,17 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>健鼎</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>3,199,000</t>
+          <t>764,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -1371,17 +1371,17 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>764,000</t>
+          <t>3,199,000</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -1415,17 +1415,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>2409</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>友達</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>10,522,121</t>
+          <t>929,659</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1437,17 +1437,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>2409</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>技嘉</t>
+          <t>友達</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>929,659</t>
+          <t>10,522,121</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -1525,17 +1525,17 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2324</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>仁寶</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>7,116,249</t>
+          <t>4,421,578</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -1547,17 +1547,17 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2324</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>仁寶</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>4,421,578</t>
+          <t>7,116,249</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -1635,17 +1635,17 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>6213</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>聯茂</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>387,000</t>
+          <t>92,000</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -1657,17 +1657,17 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>202609WVHFU6F</t>
+          <t>6213</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>富邦科技ETF期貨</t>
+          <t>聯茂</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>387,000</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -1679,17 +1679,17 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>202609WVHFU6F</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>聯強</t>
+          <t>富邦科技ETF期貨</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>2,174,107</t>
+          <t>300</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -1701,17 +1701,17 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>聯強</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>92,000</t>
+          <t>2,174,107</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -1811,17 +1811,17 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>2353</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>宏碁</t>
+          <t>可成</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>4,923,956</t>
+          <t>798,000</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
@@ -1833,17 +1833,17 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>2492</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>華新科</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>317,000</t>
+          <t>494,000</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
@@ -1855,17 +1855,17 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>可成</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>798,000</t>
+          <t>317,000</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
@@ -1877,17 +1877,17 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>2492</t>
+          <t>2353</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>華新科</t>
+          <t>宏碁</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>494,000</t>
+          <t>4,923,956</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
@@ -1965,17 +1965,17 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>2467</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>志聖</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>156,000</t>
+          <t>169,000</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
@@ -1987,17 +1987,17 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>329,000</t>
+          <t>114,000</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
@@ -2009,17 +2009,17 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>2467</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>群光</t>
+          <t>志聖</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>995,121</t>
+          <t>156,000</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
@@ -2031,17 +2031,17 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>169,000</t>
+          <t>329,000</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
@@ -2053,17 +2053,17 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>群光</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>114,000</t>
+          <t>995,121</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
@@ -2075,17 +2075,17 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>6789</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>采鈺</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>64,538</t>
+          <t>177,000</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
@@ -2097,17 +2097,17 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>6789</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>采鈺</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>177,000</t>
+          <t>64,538</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
